--- a/2_Laboratory_results.xlsx
+++ b/2_Laboratory_results.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\wrk\phd\HIS_Forms_for_Stroke_Care\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\D4YKH4\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2EE369D-6390-4F22-9A75-6B6499D2FB12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44109356-5264-4457-BE30-0C07FB9F46B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
@@ -28,63 +28,93 @@
     <t>Field</t>
   </si>
   <si>
-    <t>Field type</t>
+    <t>Field Type</t>
   </si>
   <si>
     <t>Unit</t>
   </si>
   <si>
-    <t>Calculation/validation</t>
+    <t>Calculation/Validation</t>
   </si>
   <si>
     <t>First admission laboratory</t>
   </si>
   <si>
+    <t>Glucose</t>
+  </si>
+  <si>
+    <t>Numeric field</t>
+  </si>
+  <si>
+    <t>mmol/l</t>
+  </si>
+  <si>
+    <t>INR</t>
+  </si>
+  <si>
+    <t>CRP</t>
+  </si>
+  <si>
+    <t>mg/L</t>
+  </si>
+  <si>
+    <t>Vörösvértest</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> x1012/L</t>
+  </si>
+  <si>
+    <t>Fehérvérsejt</t>
+  </si>
+  <si>
+    <t>Giga/l</t>
+  </si>
+  <si>
+    <t>Trombocita</t>
+  </si>
+  <si>
+    <t>Hematokrit</t>
+  </si>
+  <si>
+    <t>%</t>
+  </si>
+  <si>
+    <t>Hemoglobin</t>
+  </si>
+  <si>
+    <t>g/L</t>
+  </si>
+  <si>
+    <t>GOT</t>
+  </si>
+  <si>
+    <t>U/l</t>
+  </si>
+  <si>
+    <t>GPT</t>
+  </si>
+  <si>
+    <t>Natrium</t>
+  </si>
+  <si>
+    <t>mmol/L</t>
+  </si>
+  <si>
+    <t>Kalium</t>
+  </si>
+  <si>
+    <t>Kreatinin</t>
+  </si>
+  <si>
+    <t>µmol/L</t>
+  </si>
+  <si>
+    <t>Karbamid</t>
+  </si>
+  <si>
     <t>Control laboratory</t>
   </si>
   <si>
-    <t>Glucose</t>
-  </si>
-  <si>
-    <t>INR</t>
-  </si>
-  <si>
-    <t>CRP</t>
-  </si>
-  <si>
-    <t>Vörösvértest</t>
-  </si>
-  <si>
-    <t>Fehérvérsejt</t>
-  </si>
-  <si>
-    <t>Trombocita</t>
-  </si>
-  <si>
-    <t>Hematokrit</t>
-  </si>
-  <si>
-    <t>Hemoglobin</t>
-  </si>
-  <si>
-    <t>GOT</t>
-  </si>
-  <si>
-    <t>GPT</t>
-  </si>
-  <si>
-    <t>Natrium</t>
-  </si>
-  <si>
-    <t>Kalium</t>
-  </si>
-  <si>
-    <t>Kreatinin</t>
-  </si>
-  <si>
-    <t>Karbamid</t>
-  </si>
-  <si>
     <t>Összkoleszterin</t>
   </si>
   <si>
@@ -95,36 +125,6 @@
   </si>
   <si>
     <t>TSH</t>
-  </si>
-  <si>
-    <t>Numeric field</t>
-  </si>
-  <si>
-    <t>mmol/l</t>
-  </si>
-  <si>
-    <t>mg/L</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> x1012/L</t>
-  </si>
-  <si>
-    <t>Giga/l</t>
-  </si>
-  <si>
-    <t>%</t>
-  </si>
-  <si>
-    <t>g/L</t>
-  </si>
-  <si>
-    <t>U/l</t>
-  </si>
-  <si>
-    <t>mmol/L</t>
-  </si>
-  <si>
-    <t>µmol/L</t>
   </si>
   <si>
     <t>mU/l</t>
@@ -134,7 +134,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -143,20 +143,28 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="3">
@@ -195,16 +203,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -517,23 +527,23 @@
     <col min="2" max="2" width="13.4609375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.921875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="7.765625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19.3046875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.53515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
     </row>
@@ -541,215 +551,235 @@
       <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D2" t="s">
-        <v>26</v>
-      </c>
+      <c r="B2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="1"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A3" s="3"/>
-      <c r="B3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" t="s">
-        <v>25</v>
-      </c>
+      <c r="B3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A4" s="3"/>
-      <c r="B4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" t="s">
-        <v>25</v>
-      </c>
-      <c r="D4" t="s">
-        <v>27</v>
-      </c>
+      <c r="B4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" s="1"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A5" s="3"/>
-      <c r="B5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" t="s">
-        <v>25</v>
-      </c>
-      <c r="D5" t="s">
-        <v>28</v>
-      </c>
+      <c r="B5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" s="1"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A6" s="3"/>
-      <c r="B6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6" t="s">
-        <v>25</v>
-      </c>
-      <c r="D6" t="s">
-        <v>29</v>
-      </c>
+      <c r="B6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E6" s="1"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A7" s="3"/>
-      <c r="B7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C7" t="s">
-        <v>25</v>
-      </c>
-      <c r="D7" t="s">
-        <v>29</v>
-      </c>
+      <c r="B7" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E7" s="1"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A8" s="3"/>
-      <c r="B8" t="s">
-        <v>13</v>
-      </c>
-      <c r="C8" t="s">
-        <v>25</v>
-      </c>
-      <c r="D8" t="s">
-        <v>30</v>
-      </c>
+      <c r="B8" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E8" s="1"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A9" s="3"/>
-      <c r="B9" t="s">
-        <v>14</v>
-      </c>
-      <c r="C9" t="s">
-        <v>25</v>
-      </c>
-      <c r="D9" t="s">
-        <v>31</v>
-      </c>
+      <c r="B9" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E9" s="1"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A10" s="3"/>
-      <c r="B10" t="s">
-        <v>15</v>
-      </c>
-      <c r="C10" t="s">
-        <v>25</v>
-      </c>
-      <c r="D10" t="s">
-        <v>32</v>
-      </c>
+      <c r="B10" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E10" s="1"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A11" s="3"/>
-      <c r="B11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C11" t="s">
-        <v>25</v>
-      </c>
-      <c r="D11" t="s">
-        <v>32</v>
-      </c>
+      <c r="B11" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E11" s="1"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A12" s="3"/>
-      <c r="B12" t="s">
-        <v>17</v>
-      </c>
-      <c r="C12" t="s">
+      <c r="B12" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D12" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="D12" t="s">
-        <v>33</v>
-      </c>
+      <c r="E12" s="1"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A13" s="3"/>
-      <c r="B13" t="s">
-        <v>18</v>
-      </c>
-      <c r="C13" t="s">
+      <c r="B13" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D13" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="D13" t="s">
-        <v>33</v>
-      </c>
+      <c r="E13" s="1"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A14" s="3"/>
-      <c r="B14" t="s">
-        <v>19</v>
-      </c>
-      <c r="C14" t="s">
-        <v>25</v>
-      </c>
-      <c r="D14" t="s">
-        <v>34</v>
-      </c>
+      <c r="B14" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E14" s="1"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A15" s="3"/>
-      <c r="B15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C15" t="s">
+      <c r="B15" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D15" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="D15" t="s">
+      <c r="E15" s="1"/>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A16" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E16" s="1"/>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A17" s="3"/>
+      <c r="B17" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E17" s="1"/>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A18" s="3"/>
+      <c r="B18" s="1" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A16" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B16" t="s">
-        <v>21</v>
-      </c>
-      <c r="C16" t="s">
-        <v>25</v>
-      </c>
-      <c r="D16" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A17" s="3"/>
-      <c r="B17" t="s">
-        <v>22</v>
-      </c>
-      <c r="C17" t="s">
-        <v>25</v>
-      </c>
-      <c r="D17" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A18" s="3"/>
-      <c r="B18" t="s">
-        <v>23</v>
-      </c>
-      <c r="C18" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="C18" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D18" s="1"/>
+      <c r="E18" s="1"/>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A19" s="3"/>
-      <c r="B19" t="s">
-        <v>24</v>
-      </c>
-      <c r="C19" t="s">
-        <v>25</v>
-      </c>
-      <c r="D19" t="s">
+      <c r="B19" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D19" s="1" t="s">
         <v>35</v>
       </c>
+      <c r="E19" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/2_Laboratory_results.xlsx
+++ b/2_Laboratory_results.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\D4YKH4\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\wrk\phd\HIS_Forms_for_Stroke_Care\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44109356-5264-4457-BE30-0C07FB9F46B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72DE9DDC-EA81-4008-ADFA-44BB66BD6646}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -52,75 +52,33 @@
     <t>INR</t>
   </si>
   <si>
-    <t>CRP</t>
-  </si>
-  <si>
     <t>mg/L</t>
   </si>
   <si>
-    <t>Vörösvértest</t>
-  </si>
-  <si>
     <t xml:space="preserve"> x1012/L</t>
   </si>
   <si>
-    <t>Fehérvérsejt</t>
-  </si>
-  <si>
     <t>Giga/l</t>
   </si>
   <si>
-    <t>Trombocita</t>
-  </si>
-  <si>
-    <t>Hematokrit</t>
-  </si>
-  <si>
     <t>%</t>
   </si>
   <si>
-    <t>Hemoglobin</t>
-  </si>
-  <si>
     <t>g/L</t>
   </si>
   <si>
-    <t>GOT</t>
-  </si>
-  <si>
     <t>U/l</t>
   </si>
   <si>
-    <t>GPT</t>
-  </si>
-  <si>
-    <t>Natrium</t>
-  </si>
-  <si>
     <t>mmol/L</t>
   </si>
   <si>
-    <t>Kalium</t>
-  </si>
-  <si>
-    <t>Kreatinin</t>
-  </si>
-  <si>
     <t>µmol/L</t>
   </si>
   <si>
-    <t>Karbamid</t>
-  </si>
-  <si>
     <t>Control laboratory</t>
   </si>
   <si>
-    <t>Összkoleszterin</t>
-  </si>
-  <si>
-    <t>LDL</t>
-  </si>
-  <si>
     <t>HgbA1C</t>
   </si>
   <si>
@@ -128,13 +86,55 @@
   </si>
   <si>
     <t>mU/l</t>
+  </si>
+  <si>
+    <t>C-reactive protein (CRP)</t>
+  </si>
+  <si>
+    <t>Red blood cell</t>
+  </si>
+  <si>
+    <t>Leukocyte</t>
+  </si>
+  <si>
+    <t>Platelet</t>
+  </si>
+  <si>
+    <t>Haematocrit</t>
+  </si>
+  <si>
+    <t>Haemoglobin</t>
+  </si>
+  <si>
+    <t>AST</t>
+  </si>
+  <si>
+    <t>ALT</t>
+  </si>
+  <si>
+    <t>Sodium</t>
+  </si>
+  <si>
+    <t>Potassium</t>
+  </si>
+  <si>
+    <t>Creatinine</t>
+  </si>
+  <si>
+    <t>Urea</t>
+  </si>
+  <si>
+    <t>Total cholesterol</t>
+  </si>
+  <si>
+    <t>LDL cholesterol</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -151,6 +151,12 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -203,9 +209,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -213,9 +222,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normál" xfId="0" builtinId="0"/>
@@ -524,31 +531,31 @@
   <sheetFormatPr defaultColWidth="9.3828125" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="22.3046875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.4609375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.61328125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.921875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="7.765625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="19.53515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>5</v>
       </c>
       <c r="B2" s="1" t="s">
@@ -563,7 +570,7 @@
       <c r="E2" s="1"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A3" s="3"/>
+      <c r="A3" s="4"/>
       <c r="B3" s="1" t="s">
         <v>9</v>
       </c>
@@ -574,167 +581,167 @@
       <c r="E3" s="1"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A4" s="3"/>
-      <c r="B4" s="1" t="s">
+      <c r="A4" s="4"/>
+      <c r="B4" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D4" s="1" t="s">
+      <c r="E4" s="1"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A5" s="4"/>
+      <c r="B5" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="1"/>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A5" s="3"/>
-      <c r="B5" s="1" t="s">
+      <c r="E5" s="1"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A6" s="4"/>
+      <c r="B6" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D5" s="1" t="s">
+      <c r="E6" s="1"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A7" s="4"/>
+      <c r="B7" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E7" s="1"/>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A8" s="4"/>
+      <c r="B8" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="1"/>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A6" s="3"/>
-      <c r="B6" s="1" t="s">
+      <c r="E8" s="1"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A9" s="4"/>
+      <c r="B9" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D9" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D6" s="1" t="s">
+      <c r="E9" s="1"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A10" s="4"/>
+      <c r="B10" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D10" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E6" s="1"/>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A7" s="3"/>
-      <c r="B7" s="1" t="s">
+      <c r="E10" s="1"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A11" s="4"/>
+      <c r="B11" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E11" s="1"/>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A12" s="4"/>
+      <c r="B12" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D12" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C7" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E7" s="1"/>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A8" s="3"/>
-      <c r="B8" s="1" t="s">
+      <c r="E12" s="1"/>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A13" s="4"/>
+      <c r="B13" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E13" s="1"/>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A14" s="4"/>
+      <c r="B14" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D14" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C8" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D8" s="1" t="s">
+      <c r="E14" s="1"/>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A15" s="4"/>
+      <c r="B15" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E15" s="1"/>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A16" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="E8" s="1"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A9" s="3"/>
-      <c r="B9" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E9" s="1"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A10" s="3"/>
-      <c r="B10" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E10" s="1"/>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A11" s="3"/>
-      <c r="B11" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E11" s="1"/>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A12" s="3"/>
-      <c r="B12" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E12" s="1"/>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A13" s="3"/>
-      <c r="B13" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E13" s="1"/>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A14" s="3"/>
-      <c r="B14" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E14" s="1"/>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A15" s="3"/>
-      <c r="B15" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E15" s="1"/>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A16" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>31</v>
+      <c r="B16" s="6" t="s">
+        <v>34</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>7</v>
@@ -745,9 +752,9 @@
       <c r="E16" s="1"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A17" s="3"/>
-      <c r="B17" s="1" t="s">
-        <v>32</v>
+      <c r="A17" s="4"/>
+      <c r="B17" s="6" t="s">
+        <v>35</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>7</v>
@@ -758,9 +765,9 @@
       <c r="E17" s="1"/>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A18" s="3"/>
+      <c r="A18" s="4"/>
       <c r="B18" s="1" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>7</v>
@@ -769,15 +776,15 @@
       <c r="E18" s="1"/>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A19" s="3"/>
+      <c r="A19" s="4"/>
       <c r="B19" s="1" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="E19" s="1"/>
     </row>
